--- a/WeiJingShuZhi/经验表.xlsx
+++ b/WeiJingShuZhi/经验表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="27231"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29127"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\GitWeiJing\WeiJingShuZhi\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F2CC4A9E-10A3-462C-B39F-93EC0BA89159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB3877D1-269C-4269-AF5F-65A7B859DEA4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -463,7 +463,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -509,6 +509,9 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1138,7 +1141,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W71"/>
+  <dimension ref="A1:W80"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="1"/>
@@ -4565,6 +4568,225 @@
         <v>34718500</v>
       </c>
     </row>
+    <row r="72" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="17">
+        <v>71</v>
+      </c>
+      <c r="B72" s="17">
+        <f t="shared" ref="B72:B76" si="11">G72+H72+K72</f>
+        <v>91470000</v>
+      </c>
+      <c r="C72" s="17">
+        <f t="shared" ref="C72:C76" si="12">ROUND(B72,-2)</f>
+        <v>91470000</v>
+      </c>
+      <c r="D72" s="17">
+        <v>30000</v>
+      </c>
+      <c r="E72" s="17">
+        <f t="shared" ref="E72:E76" si="13">D72/$R$4</f>
+        <v>30</v>
+      </c>
+      <c r="F72" s="17">
+        <f>SUM($E$2:E72)</f>
+        <v>162.72999999999999</v>
+      </c>
+      <c r="G72" s="17">
+        <f>D72*怪物经验!C72</f>
+        <v>54300000</v>
+      </c>
+      <c r="H72" s="17">
+        <f>任务经验!F72</f>
+        <v>0</v>
+      </c>
+      <c r="I72" s="17">
+        <v>50</v>
+      </c>
+      <c r="J72" s="17">
+        <f>LOOKUP(I72,组队副本!A:A,组队副本!I:I)</f>
+        <v>247800</v>
+      </c>
+      <c r="K72" s="17">
+        <f t="shared" ref="K72:K76" si="14">J72*E72*$R$5</f>
+        <v>37170000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="17">
+        <v>72</v>
+      </c>
+      <c r="B73" s="17">
+        <f t="shared" si="11"/>
+        <v>107765000</v>
+      </c>
+      <c r="C73" s="17">
+        <f t="shared" si="12"/>
+        <v>107765000</v>
+      </c>
+      <c r="D73" s="17">
+        <v>35000</v>
+      </c>
+      <c r="E73" s="17">
+        <f t="shared" si="13"/>
+        <v>35</v>
+      </c>
+      <c r="F73" s="17">
+        <f>SUM($E$2:E73)</f>
+        <v>197.73</v>
+      </c>
+      <c r="G73" s="17">
+        <f>D73*怪物经验!C73</f>
+        <v>64400000</v>
+      </c>
+      <c r="H73" s="17">
+        <f>任务经验!F73</f>
+        <v>0</v>
+      </c>
+      <c r="I73" s="17">
+        <v>50</v>
+      </c>
+      <c r="J73" s="17">
+        <f>LOOKUP(I73,组队副本!A:A,组队副本!I:I)</f>
+        <v>247800</v>
+      </c>
+      <c r="K73" s="17">
+        <f t="shared" si="14"/>
+        <v>43365000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="17">
+        <v>73</v>
+      </c>
+      <c r="B74" s="17">
+        <f t="shared" si="11"/>
+        <v>124360000</v>
+      </c>
+      <c r="C74" s="17">
+        <f t="shared" si="12"/>
+        <v>124360000</v>
+      </c>
+      <c r="D74" s="17">
+        <v>40000</v>
+      </c>
+      <c r="E74" s="17">
+        <f t="shared" si="13"/>
+        <v>40</v>
+      </c>
+      <c r="F74" s="17">
+        <f>SUM($E$2:E74)</f>
+        <v>237.73</v>
+      </c>
+      <c r="G74" s="17">
+        <f>D74*怪物经验!C74</f>
+        <v>74800000</v>
+      </c>
+      <c r="H74" s="17">
+        <f>任务经验!F74</f>
+        <v>0</v>
+      </c>
+      <c r="I74" s="17">
+        <v>50</v>
+      </c>
+      <c r="J74" s="17">
+        <f>LOOKUP(I74,组队副本!A:A,组队副本!I:I)</f>
+        <v>247800</v>
+      </c>
+      <c r="K74" s="17">
+        <f t="shared" si="14"/>
+        <v>49560000</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="17">
+        <v>74</v>
+      </c>
+      <c r="B75" s="17">
+        <f t="shared" si="11"/>
+        <v>156950000</v>
+      </c>
+      <c r="C75" s="17">
+        <f t="shared" si="12"/>
+        <v>156950000</v>
+      </c>
+      <c r="D75" s="17">
+        <v>50000</v>
+      </c>
+      <c r="E75" s="17">
+        <f t="shared" si="13"/>
+        <v>50</v>
+      </c>
+      <c r="F75" s="17">
+        <f>SUM($E$2:E75)</f>
+        <v>287.73</v>
+      </c>
+      <c r="G75" s="17">
+        <f>D75*怪物经验!C75</f>
+        <v>95000000</v>
+      </c>
+      <c r="H75" s="17">
+        <f>任务经验!F75</f>
+        <v>0</v>
+      </c>
+      <c r="I75" s="17">
+        <v>50</v>
+      </c>
+      <c r="J75" s="17">
+        <f>LOOKUP(I75,组队副本!A:A,组队副本!I:I)</f>
+        <v>247800</v>
+      </c>
+      <c r="K75" s="17">
+        <f t="shared" si="14"/>
+        <v>61950000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="17">
+        <v>75</v>
+      </c>
+      <c r="B76" s="17">
+        <f t="shared" si="11"/>
+        <v>190140000</v>
+      </c>
+      <c r="C76" s="17">
+        <f t="shared" si="12"/>
+        <v>190140000</v>
+      </c>
+      <c r="D76" s="17">
+        <v>60000</v>
+      </c>
+      <c r="E76" s="17">
+        <f t="shared" si="13"/>
+        <v>60</v>
+      </c>
+      <c r="F76" s="17">
+        <f>SUM($E$2:E76)</f>
+        <v>347.73</v>
+      </c>
+      <c r="G76" s="17">
+        <f>D76*怪物经验!C76</f>
+        <v>115800000</v>
+      </c>
+      <c r="H76" s="17">
+        <f>任务经验!F76</f>
+        <v>0</v>
+      </c>
+      <c r="I76" s="17">
+        <v>50</v>
+      </c>
+      <c r="J76" s="17">
+        <f>LOOKUP(I76,组队副本!A:A,组队副本!I:I)</f>
+        <v>247800</v>
+      </c>
+      <c r="K76" s="17">
+        <f t="shared" si="14"/>
+        <v>74340000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="78" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="79" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="80" spans="1:13" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5983,7 +6205,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:O76"/>
+  <dimension ref="A1:O85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="9" style="4"/>
@@ -9242,14 +9464,33 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="72" spans="1:15" x14ac:dyDescent="0.2">
-      <c r="A72" s="1"/>
-      <c r="B72" s="1"/>
-      <c r="C72" s="1"/>
-      <c r="D72" s="1"/>
-      <c r="E72" s="1"/>
-      <c r="F72" s="1"/>
-      <c r="G72" s="1"/>
+    <row r="72" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A72" s="1">
+        <v>71</v>
+      </c>
+      <c r="B72" s="1">
+        <v>30</v>
+      </c>
+      <c r="C72" s="1">
+        <f t="shared" ref="C72:C76" si="16">C71+B72</f>
+        <v>1810</v>
+      </c>
+      <c r="D72" s="1">
+        <f t="shared" ref="D72:D76" si="17">C72*2</f>
+        <v>3620</v>
+      </c>
+      <c r="E72" s="1">
+        <f t="shared" ref="E72:E76" si="18">C72*2</f>
+        <v>3620</v>
+      </c>
+      <c r="F72" s="1">
+        <f t="shared" ref="F72:F76" si="19">C72*2</f>
+        <v>3620</v>
+      </c>
+      <c r="G72" s="1">
+        <f t="shared" ref="G72:G76" si="20">C72*20</f>
+        <v>36200</v>
+      </c>
       <c r="K72" s="8">
         <v>50</v>
       </c>
@@ -9269,7 +9510,33 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="73" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A73" s="1">
+        <v>72</v>
+      </c>
+      <c r="B73" s="1">
+        <v>30</v>
+      </c>
+      <c r="C73" s="1">
+        <f t="shared" si="16"/>
+        <v>1840</v>
+      </c>
+      <c r="D73" s="1">
+        <f t="shared" si="17"/>
+        <v>3680</v>
+      </c>
+      <c r="E73" s="1">
+        <f t="shared" si="18"/>
+        <v>3680</v>
+      </c>
+      <c r="F73" s="1">
+        <f t="shared" si="19"/>
+        <v>3680</v>
+      </c>
+      <c r="G73" s="1">
+        <f t="shared" si="20"/>
+        <v>36800</v>
+      </c>
       <c r="K73" s="6">
         <v>55</v>
       </c>
@@ -9289,7 +9556,33 @@
         <v>1330</v>
       </c>
     </row>
-    <row r="74" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A74" s="1">
+        <v>73</v>
+      </c>
+      <c r="B74" s="1">
+        <v>30</v>
+      </c>
+      <c r="C74" s="1">
+        <f t="shared" si="16"/>
+        <v>1870</v>
+      </c>
+      <c r="D74" s="1">
+        <f t="shared" si="17"/>
+        <v>3740</v>
+      </c>
+      <c r="E74" s="1">
+        <f t="shared" si="18"/>
+        <v>3740</v>
+      </c>
+      <c r="F74" s="1">
+        <f t="shared" si="19"/>
+        <v>3740</v>
+      </c>
+      <c r="G74" s="1">
+        <f t="shared" si="20"/>
+        <v>37400</v>
+      </c>
       <c r="K74" s="6">
         <v>56</v>
       </c>
@@ -9309,7 +9602,33 @@
         <v>27200</v>
       </c>
     </row>
-    <row r="75" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A75" s="1">
+        <v>74</v>
+      </c>
+      <c r="B75" s="1">
+        <v>30</v>
+      </c>
+      <c r="C75" s="1">
+        <f t="shared" si="16"/>
+        <v>1900</v>
+      </c>
+      <c r="D75" s="1">
+        <f t="shared" si="17"/>
+        <v>3800</v>
+      </c>
+      <c r="E75" s="1">
+        <f t="shared" si="18"/>
+        <v>3800</v>
+      </c>
+      <c r="F75" s="1">
+        <f t="shared" si="19"/>
+        <v>3800</v>
+      </c>
+      <c r="G75" s="1">
+        <f t="shared" si="20"/>
+        <v>38000</v>
+      </c>
       <c r="K75" s="6">
         <v>58</v>
       </c>
@@ -9329,7 +9648,33 @@
         <v>28400</v>
       </c>
     </row>
-    <row r="76" spans="1:15" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A76" s="1">
+        <v>75</v>
+      </c>
+      <c r="B76" s="1">
+        <v>30</v>
+      </c>
+      <c r="C76" s="1">
+        <f t="shared" si="16"/>
+        <v>1930</v>
+      </c>
+      <c r="D76" s="1">
+        <f t="shared" si="17"/>
+        <v>3860</v>
+      </c>
+      <c r="E76" s="1">
+        <f t="shared" si="18"/>
+        <v>3860</v>
+      </c>
+      <c r="F76" s="1">
+        <f t="shared" si="19"/>
+        <v>3860</v>
+      </c>
+      <c r="G76" s="1">
+        <f t="shared" si="20"/>
+        <v>38600</v>
+      </c>
       <c r="K76" s="6">
         <v>60</v>
       </c>
@@ -9349,6 +9694,152 @@
         <v>29600</v>
       </c>
     </row>
+    <row r="77" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A77" s="1">
+        <v>76</v>
+      </c>
+      <c r="B77" s="1">
+        <v>30</v>
+      </c>
+      <c r="C77" s="1">
+        <f t="shared" ref="C77:C81" si="21">C76+B77</f>
+        <v>1960</v>
+      </c>
+      <c r="D77" s="1">
+        <f t="shared" ref="D77:D81" si="22">C77*2</f>
+        <v>3920</v>
+      </c>
+      <c r="E77" s="1">
+        <f t="shared" ref="E77:E81" si="23">C77*2</f>
+        <v>3920</v>
+      </c>
+      <c r="F77" s="1">
+        <f t="shared" ref="F77:F81" si="24">C77*2</f>
+        <v>3920</v>
+      </c>
+      <c r="G77" s="1">
+        <f t="shared" ref="G77:G81" si="25">C77*20</f>
+        <v>39200</v>
+      </c>
+    </row>
+    <row r="78" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A78" s="1">
+        <v>77</v>
+      </c>
+      <c r="B78" s="1">
+        <v>30</v>
+      </c>
+      <c r="C78" s="1">
+        <f t="shared" si="21"/>
+        <v>1990</v>
+      </c>
+      <c r="D78" s="1">
+        <f t="shared" si="22"/>
+        <v>3980</v>
+      </c>
+      <c r="E78" s="1">
+        <f t="shared" si="23"/>
+        <v>3980</v>
+      </c>
+      <c r="F78" s="1">
+        <f t="shared" si="24"/>
+        <v>3980</v>
+      </c>
+      <c r="G78" s="1">
+        <f t="shared" si="25"/>
+        <v>39800</v>
+      </c>
+    </row>
+    <row r="79" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A79" s="1">
+        <v>78</v>
+      </c>
+      <c r="B79" s="1">
+        <v>30</v>
+      </c>
+      <c r="C79" s="1">
+        <f t="shared" si="21"/>
+        <v>2020</v>
+      </c>
+      <c r="D79" s="1">
+        <f t="shared" si="22"/>
+        <v>4040</v>
+      </c>
+      <c r="E79" s="1">
+        <f t="shared" si="23"/>
+        <v>4040</v>
+      </c>
+      <c r="F79" s="1">
+        <f t="shared" si="24"/>
+        <v>4040</v>
+      </c>
+      <c r="G79" s="1">
+        <f t="shared" si="25"/>
+        <v>40400</v>
+      </c>
+    </row>
+    <row r="80" spans="1:15" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A80" s="1">
+        <v>79</v>
+      </c>
+      <c r="B80" s="1">
+        <v>30</v>
+      </c>
+      <c r="C80" s="1">
+        <f t="shared" si="21"/>
+        <v>2050</v>
+      </c>
+      <c r="D80" s="1">
+        <f t="shared" si="22"/>
+        <v>4100</v>
+      </c>
+      <c r="E80" s="1">
+        <f t="shared" si="23"/>
+        <v>4100</v>
+      </c>
+      <c r="F80" s="1">
+        <f t="shared" si="24"/>
+        <v>4100</v>
+      </c>
+      <c r="G80" s="1">
+        <f t="shared" si="25"/>
+        <v>41000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A81" s="1">
+        <v>80</v>
+      </c>
+      <c r="B81" s="1">
+        <v>30</v>
+      </c>
+      <c r="C81" s="1">
+        <f t="shared" si="21"/>
+        <v>2080</v>
+      </c>
+      <c r="D81" s="1">
+        <f t="shared" si="22"/>
+        <v>4160</v>
+      </c>
+      <c r="E81" s="1">
+        <f t="shared" si="23"/>
+        <v>4160</v>
+      </c>
+      <c r="F81" s="1">
+        <f t="shared" si="24"/>
+        <v>4160</v>
+      </c>
+      <c r="G81" s="1">
+        <f t="shared" si="25"/>
+        <v>41600</v>
+      </c>
+    </row>
+    <row r="82" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A82" s="1"/>
+    </row>
+    <row r="83" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="84" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="85" spans="1:7" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <phoneticPr fontId="7" type="noConversion"/>
   <pageMargins left="0.69930555555555596" right="0.69930555555555596" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
